--- a/public/files/planilla_datos_ñandú.xlsx
+++ b/public/files/planilla_datos_ñandú.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
   <si>
-    <t>34ª ÑANDÚ - Alumnos que participan en el Certamen Intercolegial 2025</t>
+    <t>35ª ÑANDÚ - Alumnos que participan en el Certamen Intercolegial 2026</t>
   </si>
   <si>
     <t>Datos de la escuela:</t>
